--- a/table/Datas/#ArcheryRing.xlsx
+++ b/table/Datas/#ArcheryRing.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E10"/>
+  <dimension ref="A1:E13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -588,6 +588,51 @@
         <v>-10</v>
       </c>
     </row>
+    <row r="11">
+      <c r="A11" t="inlineStr"/>
+      <c r="B11" t="n">
+        <v>7</v>
+      </c>
+      <c r="C11" t="n">
+        <v>7</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="E11" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr"/>
+      <c r="B12" t="n">
+        <v>8</v>
+      </c>
+      <c r="C12" t="n">
+        <v>7</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E12" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr"/>
+      <c r="B13" t="n">
+        <v>9</v>
+      </c>
+      <c r="C13" t="n">
+        <v>7</v>
+      </c>
+      <c r="D13" t="n">
+        <v>1</v>
+      </c>
+      <c r="E13" t="n">
+        <v>5</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/table/Datas/#ArcheryRing.xlsx
+++ b/table/Datas/#ArcheryRing.xlsx
@@ -505,8 +505,8 @@
       </c>
     </row>
     <row r="5">
-      <c r="B5" t="n">
-        <v>1</v>
+      <c r="B5">
+        <v>11</v>
       </c>
       <c r="C5" t="n">
         <v>1</v>
@@ -519,8 +519,8 @@
       </c>
     </row>
     <row r="6">
-      <c r="B6" t="n">
-        <v>2</v>
+      <c r="B6">
+        <v>12</v>
       </c>
       <c r="C6" t="n">
         <v>2</v>
@@ -533,8 +533,8 @@
       </c>
     </row>
     <row r="7">
-      <c r="B7" t="n">
-        <v>3</v>
+      <c r="B7">
+        <v>13</v>
       </c>
       <c r="C7" t="n">
         <v>3</v>
@@ -547,8 +547,8 @@
       </c>
     </row>
     <row r="8">
-      <c r="B8" t="n">
-        <v>4</v>
+      <c r="B8">
+        <v>14</v>
       </c>
       <c r="C8" t="n">
         <v>4</v>
@@ -561,8 +561,8 @@
       </c>
     </row>
     <row r="9">
-      <c r="B9" t="n">
-        <v>5</v>
+      <c r="B9">
+        <v>15</v>
       </c>
       <c r="C9" t="n">
         <v>5</v>
@@ -575,8 +575,8 @@
       </c>
     </row>
     <row r="10">
-      <c r="B10" t="n">
-        <v>6</v>
+      <c r="B10">
+        <v>16</v>
       </c>
       <c r="C10" t="n">
         <v>6</v>
@@ -590,47 +590,145 @@
     </row>
     <row r="11">
       <c r="A11" t="inlineStr"/>
-      <c r="B11" t="n">
-        <v>7</v>
-      </c>
-      <c r="C11" t="n">
-        <v>7</v>
-      </c>
-      <c r="D11" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="E11" t="n">
+      <c r="B11">
+        <v>1</v>
+      </c>
+      <c r="C11">
+        <v>7</v>
+      </c>
+      <c r="D11">
+        <v>0.1</v>
+      </c>
+      <c r="E11">
         <v>10</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr"/>
-      <c r="B12" t="n">
-        <v>8</v>
-      </c>
-      <c r="C12" t="n">
-        <v>7</v>
-      </c>
-      <c r="D12" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="E12" t="n">
-        <v>8</v>
+      <c r="B12">
+        <v>2</v>
+      </c>
+      <c r="C12">
+        <v>7</v>
+      </c>
+      <c r="D12">
+        <v>0.2</v>
+      </c>
+      <c r="E12">
+        <v>9</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr"/>
-      <c r="B13" t="n">
+      <c r="B13">
+        <v>3</v>
+      </c>
+      <c r="C13">
+        <v>7</v>
+      </c>
+      <c r="D13">
+        <v>0.3</v>
+      </c>
+      <c r="E13">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14">
+        <v>4</v>
+      </c>
+      <c r="C14">
+        <v>7</v>
+      </c>
+      <c r="D14">
+        <v>0.4</v>
+      </c>
+      <c r="E14">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15">
+        <v>5</v>
+      </c>
+      <c r="C15">
+        <v>7</v>
+      </c>
+      <c r="D15">
+        <v>0.5</v>
+      </c>
+      <c r="E15">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16">
+        <v>6</v>
+      </c>
+      <c r="C16">
+        <v>7</v>
+      </c>
+      <c r="D16">
+        <v>0.6</v>
+      </c>
+      <c r="E16">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17">
+        <v>7</v>
+      </c>
+      <c r="C17">
+        <v>7</v>
+      </c>
+      <c r="D17">
+        <v>0.7</v>
+      </c>
+      <c r="E17">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18">
+        <v>8</v>
+      </c>
+      <c r="C18">
+        <v>7</v>
+      </c>
+      <c r="D18">
+        <v>0.8</v>
+      </c>
+      <c r="E18">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19">
         <v>9</v>
       </c>
-      <c r="C13" t="n">
-        <v>7</v>
-      </c>
-      <c r="D13" t="n">
-        <v>1</v>
-      </c>
-      <c r="E13" t="n">
-        <v>5</v>
+      <c r="C19">
+        <v>7</v>
+      </c>
+      <c r="D19">
+        <v>0.9</v>
+      </c>
+      <c r="E19">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20">
+        <v>10</v>
+      </c>
+      <c r="C20">
+        <v>7</v>
+      </c>
+      <c r="D20">
+        <v>1.0</v>
+      </c>
+      <c r="E20">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/table/Datas/#ArcheryRing.xlsx
+++ b/table/Datas/#ArcheryRing.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E13"/>
+  <dimension ref="A1:E14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -505,229 +505,142 @@
       </c>
     </row>
     <row r="5">
-      <c r="B5">
-        <v>11</v>
+      <c r="B5" t="n">
+        <v>1</v>
       </c>
       <c r="C5" t="n">
+        <v>7</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="E5" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" t="n">
+        <v>2</v>
+      </c>
+      <c r="C6" t="n">
+        <v>7</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="E6" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" t="n">
+        <v>3</v>
+      </c>
+      <c r="C7" t="n">
+        <v>7</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E7" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" t="n">
+        <v>4</v>
+      </c>
+      <c r="C8" t="n">
+        <v>7</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="E8" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" t="n">
+        <v>5</v>
+      </c>
+      <c r="C9" t="n">
+        <v>7</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E9" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" t="n">
+        <v>6</v>
+      </c>
+      <c r="C10" t="n">
+        <v>7</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="E10" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" t="n">
+        <v>7</v>
+      </c>
+      <c r="C11" t="n">
+        <v>7</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="E11" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" t="n">
+        <v>8</v>
+      </c>
+      <c r="C12" t="n">
+        <v>7</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="E12" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" t="n">
+        <v>9</v>
+      </c>
+      <c r="C13" t="n">
+        <v>7</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="E13" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" t="n">
+        <v>10</v>
+      </c>
+      <c r="C14" t="n">
+        <v>7</v>
+      </c>
+      <c r="D14" t="n">
         <v>1</v>
       </c>
-      <c r="D5" t="n">
-        <v>1</v>
-      </c>
-      <c r="E5" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="B6">
-        <v>12</v>
-      </c>
-      <c r="C6" t="n">
-        <v>2</v>
-      </c>
-      <c r="D6" t="n">
-        <v>1</v>
-      </c>
-      <c r="E6" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="B7">
-        <v>13</v>
-      </c>
-      <c r="C7" t="n">
-        <v>3</v>
-      </c>
-      <c r="D7" t="n">
-        <v>1</v>
-      </c>
-      <c r="E7" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="B8">
-        <v>14</v>
-      </c>
-      <c r="C8" t="n">
-        <v>4</v>
-      </c>
-      <c r="D8" t="n">
-        <v>1</v>
-      </c>
-      <c r="E8" t="n">
-        <v>-3</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="B9">
-        <v>15</v>
-      </c>
-      <c r="C9" t="n">
-        <v>5</v>
-      </c>
-      <c r="D9" t="n">
-        <v>1</v>
-      </c>
-      <c r="E9" t="n">
-        <v>-5</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="B10">
-        <v>16</v>
-      </c>
-      <c r="C10" t="n">
-        <v>6</v>
-      </c>
-      <c r="D10" t="n">
-        <v>1</v>
-      </c>
-      <c r="E10" t="n">
-        <v>-10</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr"/>
-      <c r="B11">
-        <v>1</v>
-      </c>
-      <c r="C11">
-        <v>7</v>
-      </c>
-      <c r="D11">
-        <v>0.1</v>
-      </c>
-      <c r="E11">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr"/>
-      <c r="B12">
-        <v>2</v>
-      </c>
-      <c r="C12">
-        <v>7</v>
-      </c>
-      <c r="D12">
-        <v>0.2</v>
-      </c>
-      <c r="E12">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr"/>
-      <c r="B13">
-        <v>3</v>
-      </c>
-      <c r="C13">
-        <v>7</v>
-      </c>
-      <c r="D13">
-        <v>0.3</v>
-      </c>
-      <c r="E13">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="B14">
-        <v>4</v>
-      </c>
-      <c r="C14">
-        <v>7</v>
-      </c>
-      <c r="D14">
-        <v>0.4</v>
-      </c>
-      <c r="E14">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="B15">
-        <v>5</v>
-      </c>
-      <c r="C15">
-        <v>7</v>
-      </c>
-      <c r="D15">
-        <v>0.5</v>
-      </c>
-      <c r="E15">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="B16">
-        <v>6</v>
-      </c>
-      <c r="C16">
-        <v>7</v>
-      </c>
-      <c r="D16">
-        <v>0.6</v>
-      </c>
-      <c r="E16">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="B17">
-        <v>7</v>
-      </c>
-      <c r="C17">
-        <v>7</v>
-      </c>
-      <c r="D17">
-        <v>0.7</v>
-      </c>
-      <c r="E17">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="B18">
-        <v>8</v>
-      </c>
-      <c r="C18">
-        <v>7</v>
-      </c>
-      <c r="D18">
-        <v>0.8</v>
-      </c>
-      <c r="E18">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="B19">
-        <v>9</v>
-      </c>
-      <c r="C19">
-        <v>7</v>
-      </c>
-      <c r="D19">
-        <v>0.9</v>
-      </c>
-      <c r="E19">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="B20">
-        <v>10</v>
-      </c>
-      <c r="C20">
-        <v>7</v>
-      </c>
-      <c r="D20">
-        <v>1.0</v>
-      </c>
-      <c r="E20">
+      <c r="E14" t="n">
         <v>1</v>
       </c>
     </row>

--- a/table/Datas/#ArcheryRing.xlsx
+++ b/table/Datas/#ArcheryRing.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E14"/>
+  <dimension ref="A1:E20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -644,6 +644,90 @@
         <v>1</v>
       </c>
     </row>
+    <row r="15">
+      <c r="B15" t="n">
+        <v>17</v>
+      </c>
+      <c r="C15" t="n">
+        <v>8</v>
+      </c>
+      <c r="D15" t="n">
+        <v>1</v>
+      </c>
+      <c r="E15" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" t="n">
+        <v>18</v>
+      </c>
+      <c r="C16" t="n">
+        <v>9</v>
+      </c>
+      <c r="D16" t="n">
+        <v>1</v>
+      </c>
+      <c r="E16" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" t="n">
+        <v>19</v>
+      </c>
+      <c r="C17" t="n">
+        <v>10</v>
+      </c>
+      <c r="D17" t="n">
+        <v>1</v>
+      </c>
+      <c r="E17" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" t="n">
+        <v>20</v>
+      </c>
+      <c r="C18" t="n">
+        <v>11</v>
+      </c>
+      <c r="D18" t="n">
+        <v>1</v>
+      </c>
+      <c r="E18" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" t="n">
+        <v>21</v>
+      </c>
+      <c r="C19" t="n">
+        <v>12</v>
+      </c>
+      <c r="D19" t="n">
+        <v>1</v>
+      </c>
+      <c r="E19" t="n">
+        <v>-3</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" t="n">
+        <v>22</v>
+      </c>
+      <c r="C20" t="n">
+        <v>13</v>
+      </c>
+      <c r="D20" t="n">
+        <v>1</v>
+      </c>
+      <c r="E20" t="n">
+        <v>-3</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/table/Datas/#ArcheryRing.xlsx
+++ b/table/Datas/#ArcheryRing.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E20"/>
+  <dimension ref="A1:E23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -646,10 +646,10 @@
     </row>
     <row r="15">
       <c r="B15" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="C15" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="D15" t="n">
         <v>1</v>
@@ -660,10 +660,10 @@
     </row>
     <row r="16">
       <c r="B16" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="C16" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="D16" t="n">
         <v>1</v>
@@ -674,57 +674,99 @@
     </row>
     <row r="17">
       <c r="B17" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="C17" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="D17" t="n">
         <v>1</v>
       </c>
       <c r="E17" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18">
       <c r="B18" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="C18" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="D18" t="n">
         <v>1</v>
       </c>
       <c r="E18" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="19">
       <c r="B19" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="C19" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="D19" t="n">
         <v>1</v>
       </c>
       <c r="E19" t="n">
-        <v>-3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="20">
       <c r="B20" t="n">
+        <v>28</v>
+      </c>
+      <c r="C20" t="n">
+        <v>19</v>
+      </c>
+      <c r="D20" t="n">
+        <v>1</v>
+      </c>
+      <c r="E20" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" t="n">
+        <v>29</v>
+      </c>
+      <c r="C21" t="n">
+        <v>20</v>
+      </c>
+      <c r="D21" t="n">
+        <v>1</v>
+      </c>
+      <c r="E21" t="n">
+        <v>-3</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" t="n">
+        <v>30</v>
+      </c>
+      <c r="C22" t="n">
+        <v>21</v>
+      </c>
+      <c r="D22" t="n">
+        <v>1</v>
+      </c>
+      <c r="E22" t="n">
+        <v>-3</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" t="n">
+        <v>31</v>
+      </c>
+      <c r="C23" t="n">
         <v>22</v>
       </c>
-      <c r="C20" t="n">
-        <v>13</v>
-      </c>
-      <c r="D20" t="n">
-        <v>1</v>
-      </c>
-      <c r="E20" t="n">
+      <c r="D23" t="n">
+        <v>1</v>
+      </c>
+      <c r="E23" t="n">
         <v>-3</v>
       </c>
     </row>

--- a/table/Datas/#ArcheryRing.xlsx
+++ b/table/Datas/#ArcheryRing.xlsx
@@ -739,7 +739,7 @@
         <v>1</v>
       </c>
       <c r="E21" t="n">
-        <v>-3</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="22">
@@ -753,7 +753,7 @@
         <v>1</v>
       </c>
       <c r="E22" t="n">
-        <v>-3</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="23">
@@ -767,7 +767,7 @@
         <v>1</v>
       </c>
       <c r="E23" t="n">
-        <v>-3</v>
+        <v>-4</v>
       </c>
     </row>
   </sheetData>
